--- a/output/pdf_financials_xlsx/MTA.xlsx
+++ b/output/pdf_financials_xlsx/MTA.xlsx
@@ -1276,7 +1276,7 @@
         <v>-0.448673</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.576112</v>
+        <v>-1.576112</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-1.010377</v>
@@ -1576,7 +1576,7 @@
         <v>-0.376748</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.576112</v>
+        <v>-1.576112</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-1.010377</v>
@@ -1750,7 +1750,7 @@
         <v>-0.376748</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.576112</v>
+        <v>-1.576112</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-1.010377</v>
@@ -1928,7 +1928,7 @@
         <v>-28.980615</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46.356235</v>
+        <v>-46.356235</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>-72.169786</v>
@@ -1990,7 +1990,7 @@
         <v>-0.448673</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.576112</v>
+        <v>-1.576112</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.010377</v>
@@ -2106,7 +2106,7 @@
         <v>-0.448673</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.641023</v>
+        <v>-1.511201</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.894279</v>
@@ -2240,7 +2240,7 @@
         <v>-98.68835432486466</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -5818,31 +5818,31 @@
         <v>3.672176</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.11078</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.42447</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>7.396376</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>9.153352</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>12.050932</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>13.199</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>12.93</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>13.021</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>14.371</v>
       </c>
     </row>
     <row r="93">
@@ -7265,13 +7265,13 @@
         <v>-1.018078</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.686338</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.06934800000000001</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.036293</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -10401,7 +10401,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11832,7 +11836,11 @@
           <t>Reserv es</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -16246,7 +16254,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -36062,7 +36074,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -37973,7 +37989,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -61415,10 +61435,10 @@
         </is>
       </c>
       <c r="H537" s="5" t="n">
-        <v>1.576112</v>
+        <v>-1.576112</v>
       </c>
       <c r="I537" s="5" t="n">
-        <v>1.010377</v>
+        <v>-1.010377</v>
       </c>
       <c r="J537" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MTA.xlsx
+++ b/output/pdf_financials_xlsx/MTA.xlsx
@@ -926,19 +926,19 @@
         <v>0.442788</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.307893</v>
+        <v>1.549719</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.437944</v>
+        <v>1.039577</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.169237</v>
+        <v>2.712599</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.108146</v>
+        <v>0.387782</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.181351</v>
+        <v>0.211832</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.317551</v>
@@ -984,19 +984,19 @@
         <v>-0.442788</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.307893</v>
+        <v>-1.549719</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.437944</v>
+        <v>-1.039577</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.169237</v>
+        <v>-2.712599</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.108146</v>
+        <v>-0.387782</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.181351</v>
+        <v>-0.211832</v>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000108</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.01523</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.062338</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1990,13 +1990,13 @@
         <v>-0.448673</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.576112</v>
+        <v>-1.576004</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.010377</v>
+        <v>-1.025607</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.669357</v>
+        <v>-2.731695</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-5.193915</v>
@@ -2005,7 +2005,7 @@
         <v>-0.207258</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.238684</v>
+        <v>-3.338684</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-2.364442</v>
@@ -2106,13 +2106,13 @@
         <v>-0.448673</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.511201</v>
+        <v>-1.511093</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.894279</v>
+        <v>-0.909509</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.648198</v>
+        <v>-2.710536</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-5.193317</v>
@@ -2121,7 +2121,7 @@
         <v>-0.206598</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.238684</v>
+        <v>-3.338684</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-2.364442</v>
@@ -2372,40 +2372,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.007996</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.644053</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.069898</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.261841</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.695545</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.013452</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.119198</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.004101</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.21665</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.817357</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>4.603062</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.695653</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>2.344246</v>
@@ -2488,40 +2488,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.007996</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.644053</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.069898</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.261841</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.695545</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.013452</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.119198</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.004101</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.21665</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>4.817357</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>4.603062</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>4.695653</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>2.344246</v>
@@ -3184,40 +3184,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.032389</v>
+        <v>0.024393</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.743372</v>
+        <v>0.099319</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.267952</v>
+        <v>0.198054</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.523753</v>
+        <v>0.261912</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.035408</v>
+        <v>0.339863</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.225935</v>
+        <v>0.212483</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.126477</v>
+        <v>0.007279</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.010875</v>
+        <v>0.006774</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.434209</v>
+        <v>0.217559</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.945076</v>
+        <v>0.127719</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.946926</v>
+        <v>0.343864</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.996291</v>
+        <v>0.300638</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>2.884255</v>
@@ -13440,7 +13440,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -16759,7 +16759,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -46846,7 +46846,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -47974,7 +47974,11 @@
           <t>General and administrativ e expenses 8</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -48548,7 +48552,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -49799,7 +49803,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -51420,7 +51424,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -53877,7 +53881,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -54289,7 +54293,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -56412,7 +56416,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -58196,7 +58200,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -58218,16 +58222,16 @@
         <v>1.549719</v>
       </c>
       <c r="I505" s="5" t="n">
-        <v>-1.039577</v>
+        <v>1.039577</v>
       </c>
       <c r="J505" s="5" t="n">
-        <v>-2.712599</v>
+        <v>2.712599</v>
       </c>
       <c r="K505" s="5" t="n">
-        <v>-0.387782</v>
+        <v>0.387782</v>
       </c>
       <c r="L505" s="5" t="n">
-        <v>-0.211832</v>
+        <v>0.211832</v>
       </c>
       <c r="M505" t="inlineStr">
         <is>
@@ -58499,7 +58503,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -60293,7 +60297,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -61210,7 +61214,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">

--- a/output/pdf_financials_xlsx/MTA.xlsx
+++ b/output/pdf_financials_xlsx/MTA.xlsx
@@ -764,13 +764,13 @@
         <v>0.07625999999999999</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.158491</v>
+        <v>0.169992</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.317551</v>
+        <v>0.636944</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.600604</v>
+        <v>1.10438</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>0</v>
@@ -941,10 +941,10 @@
         <v>0.211832</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.317551</v>
+        <v>0.636944</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.600604</v>
+        <v>1.10438</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>0.408524</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.364861</v>
+        <v>-0.128718</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.046706</v>
@@ -1581,11 +1581,15 @@
       <c r="F20" s="3" t="n">
         <v>-1.010377</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>-2.669357</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>-5.193915</v>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.207258</v>
@@ -1640,10 +1644,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>0.040055</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-4.758203</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
@@ -2264,7 +2268,7 @@
         <v>-19.57415653997158</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-5.949414623623022</v>
+        <v>-2.098872588529627</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0.4451807888085824</v>
@@ -2753,22 +2757,22 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.051099</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="41">
@@ -2811,22 +2815,22 @@
         <v>0.32531</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0.232042</v>
+        <v>0.283141</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>1.301173</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>1.506</v>
+        <v>1.52</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>2.811</v>
+        <v>2.815</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>2.516</v>
+        <v>2.528</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>4.379</v>
+        <v>4.413</v>
       </c>
     </row>
     <row r="42">
@@ -3217,22 +3221,22 @@
         <v>0.343864</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.300638</v>
+        <v>0.249539</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>2.884255</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.505</v>
+        <v>3.491</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.734</v>
+        <v>0.73</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.723</v>
+        <v>0.711</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.259</v>
+        <v>1.225</v>
       </c>
     </row>
     <row r="49">
@@ -6166,10 +6170,10 @@
         <v>-1.010377</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-2.669357</v>
+        <v>-2.709412</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>-5.193915</v>
+        <v>-0.435712</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-0.207258</v>
@@ -6819,25 +6823,25 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.489458</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.914258</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.818371</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>1.287</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>1.169</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>1.977</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>1.613</v>
       </c>
     </row>
     <row r="111">
@@ -23636,7 +23640,11 @@
           <t>Interest and accretion expense</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -25615,7 +25623,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -30195,7 +30207,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -32464,7 +32480,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -35389,7 +35409,11 @@
           <t>Net (loss) from continuing operations</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -39674,7 +39698,11 @@
           <t>Shares issued pursuant to private placement</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -44508,7 +44536,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -50183,7 +50215,11 @@
           <t>Deferred income tax recovery (expense) 11</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -50563,7 +50599,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -51711,7 +51751,11 @@
           <t>Current income tax recovery (expense) (Note 9)</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -51806,7 +51850,11 @@
           <t>Deferred income tax recovery (Note 9)</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -53081,7 +53129,11 @@
           <t>Deferred income tax recovery (expense) (Note 8)</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
@@ -54495,7 +54547,11 @@
           <t>Management and directors' fees (Note 10)</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E468" t="inlineStr">
         <is>
           <t>-</t>
@@ -54537,10 +54593,10 @@
         </is>
       </c>
       <c r="M468" s="5" t="n">
-        <v>-0.319393</v>
+        <v>0.319393</v>
       </c>
       <c r="N468" s="5" t="n">
-        <v>-0.503776</v>
+        <v>0.503776</v>
       </c>
       <c r="O468" t="inlineStr">
         <is>
@@ -56723,7 +56779,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
           <t>-</t>
@@ -56760,10 +56820,10 @@
         </is>
       </c>
       <c r="L490" s="5" t="n">
-        <v>-0.011501</v>
+        <v>0.011501</v>
       </c>
       <c r="M490" s="5" t="n">
-        <v>-0.025865</v>
+        <v>0.025865</v>
       </c>
       <c r="N490" t="inlineStr">
         <is>
@@ -58804,7 +58864,11 @@
           <t>Loss from discontinued operations (note 17)</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
@@ -59796,7 +59860,11 @@
           <t>Gain (loss) from discontinued operations (Note 19)</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E521" t="inlineStr">
         <is>
           <t>-</t>
@@ -63246,7 +63314,11 @@
           <t>Future income tax recovery (Note 10(a))</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E555" t="inlineStr">
         <is>
           <t>-</t>
